--- a/gstdatabase/statewise_GST_collection_2023-24.xlsx
+++ b/gstdatabase/statewise_GST_collection_2023-24.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Sep 24\GST Statistics Downloads 30th Sep 24\Downloads\Tax Collection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 30th Jun 26\Downloads\Tax Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A6937C-98C4-4800-AA6C-F6CE0B31A613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA43CF5-DE51-41AD-B93B-7E74FD53EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GST_Revenue-All_India" sheetId="3" r:id="rId1"/>
@@ -683,8 +683,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -693,33 +708,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -740,29 +728,41 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1100,18 +1100,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
     </row>
     <row r="3" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -1122,101 +1122,101 @@
       </c>
     </row>
     <row r="7" spans="1:66" x14ac:dyDescent="0.3">
-      <c r="A7" s="65"/>
-      <c r="B7" s="62" t="s">
+      <c r="A7" s="77"/>
+      <c r="B7" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="57">
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="62">
         <v>45017</v>
       </c>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="57">
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="62">
         <v>45047</v>
       </c>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="60">
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="76">
         <v>45078</v>
       </c>
-      <c r="R7" s="60"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="60"/>
-      <c r="U7" s="60"/>
-      <c r="V7" s="57">
+      <c r="R7" s="76"/>
+      <c r="S7" s="76"/>
+      <c r="T7" s="76"/>
+      <c r="U7" s="76"/>
+      <c r="V7" s="62">
         <v>45108</v>
       </c>
-      <c r="W7" s="58"/>
-      <c r="X7" s="58"/>
-      <c r="Y7" s="58"/>
-      <c r="Z7" s="59"/>
-      <c r="AA7" s="60">
+      <c r="W7" s="63"/>
+      <c r="X7" s="63"/>
+      <c r="Y7" s="63"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="76">
         <v>45139</v>
       </c>
-      <c r="AB7" s="60"/>
-      <c r="AC7" s="60"/>
-      <c r="AD7" s="60"/>
-      <c r="AE7" s="60"/>
-      <c r="AF7" s="57">
+      <c r="AB7" s="76"/>
+      <c r="AC7" s="76"/>
+      <c r="AD7" s="76"/>
+      <c r="AE7" s="76"/>
+      <c r="AF7" s="62">
         <v>45170</v>
       </c>
-      <c r="AG7" s="58"/>
-      <c r="AH7" s="58"/>
-      <c r="AI7" s="58"/>
-      <c r="AJ7" s="59"/>
-      <c r="AK7" s="60">
+      <c r="AG7" s="63"/>
+      <c r="AH7" s="63"/>
+      <c r="AI7" s="63"/>
+      <c r="AJ7" s="64"/>
+      <c r="AK7" s="76">
         <v>45200</v>
       </c>
-      <c r="AL7" s="60"/>
-      <c r="AM7" s="60"/>
-      <c r="AN7" s="60"/>
-      <c r="AO7" s="60"/>
-      <c r="AP7" s="57">
+      <c r="AL7" s="76"/>
+      <c r="AM7" s="76"/>
+      <c r="AN7" s="76"/>
+      <c r="AO7" s="76"/>
+      <c r="AP7" s="62">
         <v>45231</v>
       </c>
-      <c r="AQ7" s="58"/>
-      <c r="AR7" s="58"/>
-      <c r="AS7" s="58"/>
-      <c r="AT7" s="59"/>
-      <c r="AU7" s="57">
+      <c r="AQ7" s="63"/>
+      <c r="AR7" s="63"/>
+      <c r="AS7" s="63"/>
+      <c r="AT7" s="64"/>
+      <c r="AU7" s="62">
         <v>45261</v>
       </c>
-      <c r="AV7" s="58"/>
-      <c r="AW7" s="58"/>
-      <c r="AX7" s="58"/>
-      <c r="AY7" s="59"/>
-      <c r="AZ7" s="60">
+      <c r="AV7" s="63"/>
+      <c r="AW7" s="63"/>
+      <c r="AX7" s="63"/>
+      <c r="AY7" s="64"/>
+      <c r="AZ7" s="76">
         <v>45292</v>
       </c>
-      <c r="BA7" s="60"/>
-      <c r="BB7" s="60"/>
-      <c r="BC7" s="60"/>
-      <c r="BD7" s="60"/>
-      <c r="BE7" s="57">
+      <c r="BA7" s="76"/>
+      <c r="BB7" s="76"/>
+      <c r="BC7" s="76"/>
+      <c r="BD7" s="76"/>
+      <c r="BE7" s="62">
         <v>45323</v>
       </c>
-      <c r="BF7" s="58"/>
-      <c r="BG7" s="58"/>
-      <c r="BH7" s="58"/>
-      <c r="BI7" s="59"/>
-      <c r="BJ7" s="60">
+      <c r="BF7" s="63"/>
+      <c r="BG7" s="63"/>
+      <c r="BH7" s="63"/>
+      <c r="BI7" s="64"/>
+      <c r="BJ7" s="76">
         <v>45352</v>
       </c>
-      <c r="BK7" s="60"/>
-      <c r="BL7" s="60"/>
-      <c r="BM7" s="60"/>
-      <c r="BN7" s="60"/>
+      <c r="BK7" s="76"/>
+      <c r="BL7" s="76"/>
+      <c r="BM7" s="76"/>
+      <c r="BN7" s="76"/>
     </row>
     <row r="8" spans="1:66" x14ac:dyDescent="0.3">
-      <c r="A8" s="65"/>
+      <c r="A8" s="77"/>
       <c r="B8" s="12" t="s">
         <v>2</v>
       </c>
@@ -3405,24 +3405,18 @@
       </c>
     </row>
     <row r="23" spans="1:66" x14ac:dyDescent="0.3">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="L7:P7"/>
-    <mergeCell ref="Q7:U7"/>
-    <mergeCell ref="A7:A8"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="AU7:AY7"/>
     <mergeCell ref="AZ7:BD7"/>
@@ -3433,6 +3427,12 @@
     <mergeCell ref="AF7:AJ7"/>
     <mergeCell ref="AK7:AO7"/>
     <mergeCell ref="AP7:AT7"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:P7"/>
+    <mergeCell ref="Q7:U7"/>
+    <mergeCell ref="A7:A8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -3480,8 +3480,8 @@
       <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A2" s="66"/>
-      <c r="B2" s="66"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
     </row>
     <row r="3" spans="1:67" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
@@ -3489,114 +3489,114 @@
       </c>
     </row>
     <row r="4" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="67"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="57">
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="62">
         <v>45017</v>
       </c>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="57">
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="62">
         <v>45047</v>
       </c>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="59"/>
-      <c r="R5" s="57">
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="62">
         <v>45078</v>
       </c>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="59"/>
-      <c r="W5" s="57">
+      <c r="S5" s="63"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="63"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="62">
         <v>45108</v>
       </c>
-      <c r="X5" s="58"/>
-      <c r="Y5" s="58"/>
-      <c r="Z5" s="58"/>
-      <c r="AA5" s="59"/>
-      <c r="AB5" s="57">
+      <c r="X5" s="63"/>
+      <c r="Y5" s="63"/>
+      <c r="Z5" s="63"/>
+      <c r="AA5" s="64"/>
+      <c r="AB5" s="62">
         <v>45139</v>
       </c>
-      <c r="AC5" s="58"/>
-      <c r="AD5" s="58"/>
-      <c r="AE5" s="58"/>
-      <c r="AF5" s="59"/>
-      <c r="AG5" s="57">
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="63"/>
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="64"/>
+      <c r="AG5" s="62">
         <v>45170</v>
       </c>
-      <c r="AH5" s="58"/>
-      <c r="AI5" s="58"/>
-      <c r="AJ5" s="58"/>
-      <c r="AK5" s="59"/>
-      <c r="AL5" s="57">
+      <c r="AH5" s="63"/>
+      <c r="AI5" s="63"/>
+      <c r="AJ5" s="63"/>
+      <c r="AK5" s="64"/>
+      <c r="AL5" s="62">
         <v>45200</v>
       </c>
-      <c r="AM5" s="58"/>
-      <c r="AN5" s="58"/>
-      <c r="AO5" s="58"/>
-      <c r="AP5" s="59"/>
-      <c r="AQ5" s="57">
+      <c r="AM5" s="63"/>
+      <c r="AN5" s="63"/>
+      <c r="AO5" s="63"/>
+      <c r="AP5" s="64"/>
+      <c r="AQ5" s="62">
         <v>45231</v>
       </c>
-      <c r="AR5" s="58"/>
-      <c r="AS5" s="58"/>
-      <c r="AT5" s="58"/>
-      <c r="AU5" s="59"/>
-      <c r="AV5" s="57">
+      <c r="AR5" s="63"/>
+      <c r="AS5" s="63"/>
+      <c r="AT5" s="63"/>
+      <c r="AU5" s="64"/>
+      <c r="AV5" s="62">
         <v>45261</v>
       </c>
-      <c r="AW5" s="58"/>
-      <c r="AX5" s="58"/>
-      <c r="AY5" s="58"/>
-      <c r="AZ5" s="59"/>
-      <c r="BA5" s="57">
+      <c r="AW5" s="63"/>
+      <c r="AX5" s="63"/>
+      <c r="AY5" s="63"/>
+      <c r="AZ5" s="64"/>
+      <c r="BA5" s="62">
         <v>45292</v>
       </c>
-      <c r="BB5" s="58"/>
-      <c r="BC5" s="58"/>
-      <c r="BD5" s="58"/>
-      <c r="BE5" s="59"/>
-      <c r="BF5" s="57">
+      <c r="BB5" s="63"/>
+      <c r="BC5" s="63"/>
+      <c r="BD5" s="63"/>
+      <c r="BE5" s="64"/>
+      <c r="BF5" s="62">
         <v>45323</v>
       </c>
-      <c r="BG5" s="58"/>
-      <c r="BH5" s="58"/>
-      <c r="BI5" s="58"/>
-      <c r="BJ5" s="59"/>
-      <c r="BK5" s="57">
+      <c r="BG5" s="63"/>
+      <c r="BH5" s="63"/>
+      <c r="BI5" s="63"/>
+      <c r="BJ5" s="64"/>
+      <c r="BK5" s="62">
         <v>45352</v>
       </c>
-      <c r="BL5" s="58"/>
-      <c r="BM5" s="58"/>
-      <c r="BN5" s="58"/>
-      <c r="BO5" s="58"/>
+      <c r="BL5" s="63"/>
+      <c r="BM5" s="63"/>
+      <c r="BN5" s="63"/>
+      <c r="BO5" s="63"/>
     </row>
     <row r="6" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
-      <c r="B6" s="71"/>
+      <c r="A6" s="67"/>
+      <c r="B6" s="67"/>
       <c r="C6" s="44" t="s">
         <v>2</v>
       </c>
@@ -12374,10 +12374,10 @@
       </c>
     </row>
     <row r="46" spans="1:67" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="70" t="s">
+      <c r="A46" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="70"/>
+      <c r="B46" s="66"/>
       <c r="C46" s="46">
         <f>SUM(C7:C45)</f>
         <v>375710.42999999993</v>
@@ -12647,10 +12647,10 @@
       <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A48" s="69" t="s">
+      <c r="A48" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="69"/>
+      <c r="B48" s="65"/>
       <c r="C48" s="39">
         <f t="shared" ref="C48" si="27">H48+M48+R48</f>
         <v>0</v>
@@ -12911,10 +12911,10 @@
       <c r="V49" s="23"/>
     </row>
     <row r="50" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A50" s="68" t="s">
+      <c r="A50" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="68"/>
+      <c r="B50" s="61"/>
       <c r="C50" s="24">
         <f t="shared" ref="C50:BN50" si="55">C48+C46</f>
         <v>375710.42999999993</v>
@@ -13194,18 +13194,28 @@
       <c r="AK53" s="10"/>
     </row>
     <row r="54" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="B54" s="56" t="s">
+      <c r="B54" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="56"/>
-      <c r="D54" s="56"/>
-      <c r="E54" s="56"/>
-      <c r="F54" s="56"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="56"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="AV5:AZ5"/>
+    <mergeCell ref="BA5:BE5"/>
+    <mergeCell ref="BF5:BJ5"/>
+    <mergeCell ref="BK5:BO5"/>
+    <mergeCell ref="W5:AA5"/>
+    <mergeCell ref="AB5:AF5"/>
+    <mergeCell ref="AG5:AK5"/>
+    <mergeCell ref="AL5:AP5"/>
+    <mergeCell ref="AQ5:AU5"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A50:B50"/>
@@ -13217,16 +13227,6 @@
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="AV5:AZ5"/>
-    <mergeCell ref="BA5:BE5"/>
-    <mergeCell ref="BF5:BJ5"/>
-    <mergeCell ref="BK5:BO5"/>
-    <mergeCell ref="W5:AA5"/>
-    <mergeCell ref="AB5:AF5"/>
-    <mergeCell ref="AG5:AK5"/>
-    <mergeCell ref="AL5:AP5"/>
-    <mergeCell ref="AQ5:AU5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="45" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -13264,27 +13264,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A2" s="66"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
     </row>
     <row r="3" spans="1:67" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
@@ -13292,117 +13292,117 @@
       </c>
     </row>
     <row r="4" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
     </row>
     <row r="7" spans="1:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="75">
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="79">
         <v>45017</v>
       </c>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="75">
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79">
         <v>45047</v>
       </c>
-      <c r="N7" s="75"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75">
+      <c r="N7" s="79"/>
+      <c r="O7" s="79"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="79"/>
+      <c r="R7" s="79">
         <v>45078</v>
       </c>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75">
+      <c r="S7" s="79"/>
+      <c r="T7" s="79"/>
+      <c r="U7" s="79"/>
+      <c r="V7" s="79"/>
+      <c r="W7" s="79">
         <v>45108</v>
       </c>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="75"/>
-      <c r="Z7" s="75"/>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="75">
+      <c r="X7" s="79"/>
+      <c r="Y7" s="79"/>
+      <c r="Z7" s="79"/>
+      <c r="AA7" s="79"/>
+      <c r="AB7" s="79">
         <v>45139</v>
       </c>
-      <c r="AC7" s="75"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="75"/>
-      <c r="AF7" s="75"/>
-      <c r="AG7" s="75">
+      <c r="AC7" s="79"/>
+      <c r="AD7" s="79"/>
+      <c r="AE7" s="79"/>
+      <c r="AF7" s="79"/>
+      <c r="AG7" s="79">
         <v>45170</v>
       </c>
-      <c r="AH7" s="75"/>
-      <c r="AI7" s="75"/>
-      <c r="AJ7" s="75"/>
-      <c r="AK7" s="75"/>
-      <c r="AL7" s="75">
+      <c r="AH7" s="79"/>
+      <c r="AI7" s="79"/>
+      <c r="AJ7" s="79"/>
+      <c r="AK7" s="79"/>
+      <c r="AL7" s="79">
         <v>45200</v>
       </c>
-      <c r="AM7" s="75"/>
-      <c r="AN7" s="75"/>
-      <c r="AO7" s="75"/>
-      <c r="AP7" s="75"/>
-      <c r="AQ7" s="75">
+      <c r="AM7" s="79"/>
+      <c r="AN7" s="79"/>
+      <c r="AO7" s="79"/>
+      <c r="AP7" s="79"/>
+      <c r="AQ7" s="79">
         <v>45231</v>
       </c>
-      <c r="AR7" s="75"/>
-      <c r="AS7" s="75"/>
-      <c r="AT7" s="75"/>
-      <c r="AU7" s="75"/>
-      <c r="AV7" s="75">
+      <c r="AR7" s="79"/>
+      <c r="AS7" s="79"/>
+      <c r="AT7" s="79"/>
+      <c r="AU7" s="79"/>
+      <c r="AV7" s="79">
         <v>45261</v>
       </c>
-      <c r="AW7" s="75"/>
-      <c r="AX7" s="75"/>
-      <c r="AY7" s="75"/>
-      <c r="AZ7" s="75"/>
-      <c r="BA7" s="75">
+      <c r="AW7" s="79"/>
+      <c r="AX7" s="79"/>
+      <c r="AY7" s="79"/>
+      <c r="AZ7" s="79"/>
+      <c r="BA7" s="79">
         <v>45292</v>
       </c>
-      <c r="BB7" s="75"/>
-      <c r="BC7" s="75"/>
-      <c r="BD7" s="75"/>
-      <c r="BE7" s="75"/>
-      <c r="BF7" s="75">
+      <c r="BB7" s="79"/>
+      <c r="BC7" s="79"/>
+      <c r="BD7" s="79"/>
+      <c r="BE7" s="79"/>
+      <c r="BF7" s="79">
         <v>45323</v>
       </c>
-      <c r="BG7" s="75"/>
-      <c r="BH7" s="75"/>
-      <c r="BI7" s="75"/>
-      <c r="BJ7" s="75"/>
-      <c r="BK7" s="75">
+      <c r="BG7" s="79"/>
+      <c r="BH7" s="79"/>
+      <c r="BI7" s="79"/>
+      <c r="BJ7" s="79"/>
+      <c r="BK7" s="79">
         <v>45352</v>
       </c>
-      <c r="BL7" s="75"/>
-      <c r="BM7" s="75"/>
-      <c r="BN7" s="75"/>
-      <c r="BO7" s="75"/>
+      <c r="BL7" s="79"/>
+      <c r="BM7" s="79"/>
+      <c r="BN7" s="79"/>
+      <c r="BO7" s="79"/>
     </row>
     <row r="8" spans="1:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="76"/>
-      <c r="B8" s="76"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="81"/>
       <c r="C8" s="50" t="s">
         <v>2</v>
       </c>
@@ -21203,209 +21203,209 @@
       <c r="BN46" s="20"/>
       <c r="BO46" s="20"/>
     </row>
-    <row r="47" spans="1:67" s="82" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="79" t="s">
+    <row r="47" spans="1:67" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="79"/>
-      <c r="C47" s="80">
+      <c r="B47" s="82"/>
+      <c r="C47" s="56">
         <f t="shared" si="1"/>
         <v>30305.826462101999</v>
       </c>
-      <c r="D47" s="80">
+      <c r="D47" s="56">
         <f t="shared" si="1"/>
         <v>37540.907393994996</v>
       </c>
-      <c r="E47" s="80">
+      <c r="E47" s="56">
         <f t="shared" si="1"/>
         <v>53406.321567988001</v>
       </c>
-      <c r="F47" s="80">
+      <c r="F47" s="56">
         <f t="shared" si="1"/>
         <v>2340.6153723560005</v>
       </c>
-      <c r="G47" s="80">
+      <c r="G47" s="56">
         <f t="shared" si="1"/>
         <v>123593.6706826</v>
       </c>
-      <c r="H47" s="81">
+      <c r="H47" s="57">
         <v>3019.310787588</v>
       </c>
-      <c r="I47" s="81">
+      <c r="I47" s="57">
         <v>3634.6207066490001</v>
       </c>
-      <c r="J47" s="81">
+      <c r="J47" s="57">
         <v>5446.3086929150013</v>
       </c>
-      <c r="K47" s="81">
+      <c r="K47" s="57">
         <v>149.47194229000002</v>
       </c>
-      <c r="L47" s="81">
+      <c r="L47" s="57">
         <v>12249.7120977</v>
       </c>
-      <c r="M47" s="81">
+      <c r="M47" s="57">
         <v>3057.5317359159999</v>
       </c>
-      <c r="N47" s="81">
+      <c r="N47" s="57">
         <v>3843.7539225529995</v>
       </c>
-      <c r="O47" s="81">
+      <c r="O47" s="57">
         <v>5924.7333940240014</v>
       </c>
-      <c r="P47" s="81">
+      <c r="P47" s="57">
         <v>191.471480856</v>
       </c>
-      <c r="Q47" s="81">
+      <c r="Q47" s="57">
         <v>13017.490551499999</v>
       </c>
-      <c r="R47" s="81">
+      <c r="R47" s="57">
         <v>2246.3988242570003</v>
       </c>
-      <c r="S47" s="81">
+      <c r="S47" s="57">
         <v>2734.8206829390001</v>
       </c>
-      <c r="T47" s="81">
+      <c r="T47" s="57">
         <v>4244.3325634759985</v>
       </c>
-      <c r="U47" s="81">
+      <c r="U47" s="57">
         <v>150.42899119200001</v>
       </c>
-      <c r="V47" s="81">
+      <c r="V47" s="57">
         <v>9375.981045999999</v>
       </c>
-      <c r="W47" s="81">
+      <c r="W47" s="57">
         <v>2881.3787523609999</v>
       </c>
-      <c r="X47" s="81">
+      <c r="X47" s="57">
         <v>3586.8419494299992</v>
       </c>
-      <c r="Y47" s="81">
+      <c r="Y47" s="57">
         <v>5140.4514973389987</v>
       </c>
-      <c r="Z47" s="81">
+      <c r="Z47" s="57">
         <v>248.17460532800001</v>
       </c>
-      <c r="AA47" s="81">
+      <c r="AA47" s="57">
         <v>11856.846789100002</v>
       </c>
-      <c r="AB47" s="81">
+      <c r="AB47" s="57">
         <v>2338.8621932439996</v>
       </c>
-      <c r="AC47" s="81">
+      <c r="AC47" s="57">
         <v>2881.2912577599996</v>
       </c>
-      <c r="AD47" s="81">
+      <c r="AD47" s="57">
         <v>3593.3045455599995</v>
       </c>
-      <c r="AE47" s="81">
+      <c r="AE47" s="57">
         <v>147.83531526100001</v>
       </c>
-      <c r="AF47" s="81">
+      <c r="AF47" s="57">
         <v>8961.293299500001</v>
       </c>
-      <c r="AG47" s="81">
+      <c r="AG47" s="57">
         <v>2188.9289936890004</v>
       </c>
-      <c r="AH47" s="81">
+      <c r="AH47" s="57">
         <v>2777.3890421360006</v>
       </c>
-      <c r="AI47" s="81">
+      <c r="AI47" s="57">
         <v>3499.9775286449999</v>
       </c>
-      <c r="AJ47" s="81">
+      <c r="AJ47" s="57">
         <v>126.48564616200002</v>
       </c>
-      <c r="AK47" s="81">
+      <c r="AK47" s="57">
         <v>8592.7812028999997</v>
       </c>
-      <c r="AL47" s="81">
+      <c r="AL47" s="57">
         <v>1769.6280071970004</v>
       </c>
-      <c r="AM47" s="81">
+      <c r="AM47" s="57">
         <v>2235.9383614819999</v>
       </c>
-      <c r="AN47" s="81">
+      <c r="AN47" s="57">
         <v>3201.1161317850001</v>
       </c>
-      <c r="AO47" s="81">
+      <c r="AO47" s="57">
         <v>145.176538204</v>
       </c>
-      <c r="AP47" s="81">
+      <c r="AP47" s="57">
         <v>7351.8590375000013</v>
       </c>
-      <c r="AQ47" s="81">
+      <c r="AQ47" s="57">
         <v>2952.3383088360001</v>
       </c>
-      <c r="AR47" s="81">
+      <c r="AR47" s="57">
         <v>3521.5228192339991</v>
       </c>
-      <c r="AS47" s="81">
+      <c r="AS47" s="57">
         <v>5797.3068757530018</v>
       </c>
-      <c r="AT47" s="81">
+      <c r="AT47" s="57">
         <v>303.57578561900004</v>
       </c>
-      <c r="AU47" s="81">
+      <c r="AU47" s="57">
         <v>12574.743782400003</v>
       </c>
-      <c r="AV47" s="81">
+      <c r="AV47" s="57">
         <v>2082.0052630389996</v>
       </c>
-      <c r="AW47" s="81">
+      <c r="AW47" s="57">
         <v>2550.0858250910001</v>
       </c>
-      <c r="AX47" s="81">
+      <c r="AX47" s="57">
         <v>4069.5338091670005</v>
       </c>
-      <c r="AY47" s="81">
+      <c r="AY47" s="57">
         <v>132.29573746199998</v>
       </c>
-      <c r="AZ47" s="81">
+      <c r="AZ47" s="57">
         <v>8833.9206121000007</v>
       </c>
-      <c r="BA47" s="81">
+      <c r="BA47" s="57">
         <v>2606.5910979410005</v>
       </c>
-      <c r="BB47" s="81">
+      <c r="BB47" s="57">
         <v>3364.5714087279994</v>
       </c>
-      <c r="BC47" s="81">
+      <c r="BC47" s="57">
         <v>4701.1668296889993</v>
       </c>
-      <c r="BD47" s="81">
+      <c r="BD47" s="57">
         <v>172.27010205200003</v>
       </c>
-      <c r="BE47" s="81">
+      <c r="BE47" s="57">
         <v>10844.599443799996</v>
       </c>
-      <c r="BF47" s="81">
+      <c r="BF47" s="57">
         <v>2248.1145833679993</v>
       </c>
-      <c r="BG47" s="81">
+      <c r="BG47" s="57">
         <v>2866.6454844730006</v>
       </c>
-      <c r="BH47" s="81">
+      <c r="BH47" s="57">
         <v>3310.7599635199999</v>
       </c>
-      <c r="BI47" s="81">
+      <c r="BI47" s="57">
         <v>296.34530157099994</v>
       </c>
-      <c r="BJ47" s="81">
+      <c r="BJ47" s="57">
         <v>8721.8653221000004</v>
       </c>
-      <c r="BK47" s="81">
+      <c r="BK47" s="57">
         <v>2914.737914666001</v>
       </c>
-      <c r="BL47" s="81">
+      <c r="BL47" s="57">
         <v>3543.4259335199999</v>
       </c>
-      <c r="BM47" s="81">
+      <c r="BM47" s="57">
         <v>4477.329736114998</v>
       </c>
-      <c r="BN47" s="81">
+      <c r="BN47" s="57">
         <v>277.08392635899997</v>
       </c>
-      <c r="BO47" s="81">
+      <c r="BO47" s="57">
         <v>11212.577498000002</v>
       </c>
     </row>
@@ -21482,10 +21482,10 @@
       <c r="BO48" s="37"/>
     </row>
     <row r="49" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A49" s="78" t="s">
+      <c r="A49" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="78"/>
+      <c r="B49" s="80"/>
       <c r="C49" s="42">
         <f t="shared" ref="C49:D49" si="2">H49+M49+R49</f>
         <v>0</v>
@@ -21724,10 +21724,10 @@
       <c r="V50" s="35"/>
     </row>
     <row r="51" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A51" s="68" t="s">
+      <c r="A51" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="B51" s="68"/>
+      <c r="B51" s="61"/>
       <c r="C51" s="24">
         <f>C47+C49</f>
         <v>30305.826462101999</v>
@@ -22002,21 +22002,32 @@
       </c>
     </row>
     <row r="55" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="B55" s="56" t="s">
+      <c r="B55" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="56"/>
-      <c r="F55" s="56"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C58:F70">
     <sortCondition ref="C58:C70"/>
   </sortState>
   <mergeCells count="22">
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="BA7:BE7"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="BK7:BO7"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="AG7:AK7"/>
+    <mergeCell ref="AL7:AP7"/>
+    <mergeCell ref="AQ7:AU7"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
@@ -22028,17 +22039,6 @@
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="H7:L7"/>
     <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="BA7:BE7"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="BK7:BO7"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="AG7:AK7"/>
-    <mergeCell ref="AL7:AP7"/>
-    <mergeCell ref="AQ7:AU7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
